--- a/Objective 2/Data/PEFL-5/PEFL_xys.xlsx
+++ b/Objective 2/Data/PEFL-5/PEFL_xys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/PEFL-5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D4435ED-2293-F640-BC9F-A940B83EC34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{2D4435ED-2293-F640-BC9F-A940B83EC34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{185111A4-DBA6-604D-B07D-018589B91C1B}"/>
   <bookViews>
     <workbookView xWindow="5260" yWindow="-17080" windowWidth="26040" windowHeight="14180" xr2:uid="{081034C5-BE5B-B94E-828C-09FE9D8E08EA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="9">
   <si>
     <t>Genus</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>upper</t>
+  </si>
+  <si>
+    <t>Tag #</t>
   </si>
 </sst>
 </file>
@@ -507,329 +510,386 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE25639-0ACC-644A-BBB5-5BE1A365C77D}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="34">
+    <row r="1" spans="1:6" ht="34">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4">
+        <v>2824</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5">
+      <c r="D2" s="5">
         <v>2370100</v>
       </c>
-      <c r="D2" s="6">
+      <c r="E2" s="6">
         <v>43.179839999999999</v>
       </c>
-      <c r="E2" s="6">
+      <c r="F2" s="6">
         <v>-79.055999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4">
+        <v>2837</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5">
+      <c r="D3" s="5">
         <v>5660141</v>
       </c>
-      <c r="D3" s="7">
+      <c r="E3" s="7">
         <v>43.179839999999999</v>
       </c>
-      <c r="E3" s="7">
+      <c r="F3" s="7">
         <v>-79.055999999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4">
+        <v>3361</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5">
+      <c r="D4" s="5">
         <v>3031208</v>
       </c>
-      <c r="D4" s="7">
+      <c r="E4" s="7">
         <v>43.187469999999998</v>
       </c>
-      <c r="E4" s="7">
+      <c r="F4" s="7">
         <v>-79.056569999999994</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4">
+        <v>3366</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5">
+      <c r="D5" s="5">
         <v>3241672</v>
       </c>
-      <c r="D5" s="6">
+      <c r="E5" s="6">
         <v>43.187469999999998</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="6">
         <v>-79.056569999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4">
+        <v>3368</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5">
+      <c r="D6" s="5">
         <v>3489231</v>
       </c>
-      <c r="D6" s="6">
+      <c r="E6" s="6">
         <v>43.187469999999998</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="6">
         <v>-79.056569999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="4" t="s">
-        <v>5</v>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4">
+        <v>3540</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5">
+      <c r="D7" s="5">
         <v>3709608</v>
       </c>
-      <c r="D7" s="6">
+      <c r="E7" s="6">
         <v>43.179839999999999</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="6">
         <v>-79.055999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4">
+        <v>3544</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5">
+      <c r="D8" s="5">
         <v>4794232</v>
       </c>
-      <c r="D8" s="6">
+      <c r="E8" s="6">
         <v>43.179839999999999</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="6">
         <v>-79.055999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="4" t="s">
-        <v>5</v>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4">
+        <v>3549</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5">
+      <c r="D9" s="5">
         <v>2986685</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="6">
         <v>43.170400000000001</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="6">
         <v>-79.05592</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="4" t="s">
-        <v>5</v>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4">
+        <v>3551</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="5">
+      <c r="D10" s="5">
         <v>4325964</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="6">
         <v>43.170400000000001</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="6">
         <v>-79.05592</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
-        <v>5</v>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4">
+        <v>2802</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5">
+      <c r="D11" s="5">
         <v>2112535</v>
       </c>
-      <c r="D11" s="7">
+      <c r="E11" s="7">
         <v>42.949339999999999</v>
       </c>
-      <c r="E11" s="7">
+      <c r="F11" s="7">
         <v>-78.947159999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
-        <v>5</v>
+    <row r="12" spans="1:6">
+      <c r="A12" s="4">
+        <v>2805</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="5">
+      <c r="D12" s="5">
         <v>1992104</v>
       </c>
-      <c r="D12" s="7">
+      <c r="E12" s="7">
         <v>42.949339999999999</v>
       </c>
-      <c r="E12" s="7">
+      <c r="F12" s="7">
         <v>-78.947159999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
-        <v>5</v>
+    <row r="13" spans="1:6">
+      <c r="A13" s="4">
+        <v>2816</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="5">
+      <c r="D13" s="5">
         <v>2675953</v>
       </c>
-      <c r="D13" s="7">
+      <c r="E13" s="7">
         <v>42.949339999999999</v>
       </c>
-      <c r="E13" s="7">
+      <c r="F13" s="7">
         <v>-78.947159999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
-        <v>5</v>
+    <row r="14" spans="1:6">
+      <c r="A14" s="4">
+        <v>2817</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="5">
+      <c r="D14" s="5">
         <v>3208015</v>
       </c>
-      <c r="D14" s="7">
+      <c r="E14" s="7">
         <v>42.949339999999999</v>
       </c>
-      <c r="E14" s="7">
+      <c r="F14" s="7">
         <v>-78.947159999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
-        <v>5</v>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4">
+        <v>2818</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="5">
+      <c r="D15" s="5">
         <v>1571401</v>
       </c>
-      <c r="D15" s="7">
+      <c r="E15" s="7">
         <v>42.949339999999999</v>
       </c>
-      <c r="E15" s="7">
+      <c r="F15" s="7">
         <v>-78.947159999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
-        <v>5</v>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4">
+        <v>2892</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="5">
+      <c r="D16" s="5">
         <v>2814212</v>
       </c>
-      <c r="D16" s="6">
+      <c r="E16" s="6">
         <v>42.949339999999999</v>
       </c>
-      <c r="E16" s="6">
+      <c r="F16" s="6">
         <v>-78.947159999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
-        <v>5</v>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4">
+        <v>2894</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="5">
+      <c r="D17" s="5">
         <v>2600915</v>
       </c>
-      <c r="D17" s="7">
+      <c r="E17" s="7">
         <v>42.949339999999999</v>
       </c>
-      <c r="E17" s="7">
+      <c r="F17" s="7">
         <v>-78.947159999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
-        <v>5</v>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4">
+        <v>2907</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="5">
+      <c r="D18" s="5">
         <v>2659592</v>
       </c>
-      <c r="D18" s="7">
+      <c r="E18" s="7">
         <v>42.949339999999999</v>
       </c>
-      <c r="E18" s="7">
+      <c r="F18" s="7">
         <v>-78.947159999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4" t="s">
-        <v>5</v>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4">
+        <v>2912</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="5">
+      <c r="D19" s="5">
         <v>4070657</v>
       </c>
-      <c r="D19" s="7">
+      <c r="E19" s="7">
         <v>42.949339999999999</v>
       </c>
-      <c r="E19" s="7">
+      <c r="F19" s="7">
         <v>-78.947159999999997</v>
       </c>
     </row>
